--- a/data/100M_registrations.xlsx
+++ b/data/100M_registrations.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willi\PycharmProjects\Sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2EE43F-D8C7-427E-B288-ECA372A11122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910916EB-18EE-4738-AC7B-D4F906982E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="9840" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2025" sheetId="1" r:id="rId1"/>
+    <sheet name="2024" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="174">
   <si>
     <t>Race</t>
   </si>
@@ -529,6 +541,24 @@
   </si>
   <si>
     <t>Flagstaff, AZ</t>
+  </si>
+  <si>
+    <t>Grit Ultra Endurance</t>
+  </si>
+  <si>
+    <t>West Columbia, TX</t>
+  </si>
+  <si>
+    <t>Arbuckle 100</t>
+  </si>
+  <si>
+    <t>Davis, OK</t>
+  </si>
+  <si>
+    <t>Urban Adventure Race</t>
+  </si>
+  <si>
+    <t>Tulsa, OK</t>
   </si>
 </sst>
 </file>
@@ -872,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
@@ -2075,7 +2105,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B60" t="s">
         <v>77</v>
@@ -2084,18 +2114,18 @@
         <v>9</v>
       </c>
       <c r="D60" s="2">
-        <v>45634</v>
+        <v>45597</v>
       </c>
       <c r="G60" s="2">
-        <v>45492</v>
+        <v>45863</v>
       </c>
       <c r="H60" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B61" t="s">
         <v>77</v>
@@ -2104,153 +2134,150 @@
         <v>9</v>
       </c>
       <c r="D61" s="2">
-        <v>45597</v>
+        <v>45628</v>
       </c>
       <c r="G61" s="2">
-        <v>45863</v>
+        <v>45864</v>
       </c>
       <c r="H61" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B62" t="s">
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D62" s="2">
-        <v>45628</v>
+        <v>45534</v>
+      </c>
+      <c r="E62" s="2">
+        <v>45550</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45553</v>
       </c>
       <c r="G62" s="2">
-        <v>45864</v>
+        <v>45871</v>
       </c>
       <c r="H62" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B63" t="s">
         <v>77</v>
       </c>
       <c r="C63" t="s">
-        <v>48</v>
-      </c>
-      <c r="D63" s="2">
-        <v>45534</v>
-      </c>
-      <c r="E63" s="2">
-        <v>45550</v>
-      </c>
-      <c r="F63" s="2">
-        <v>45553</v>
+        <v>9</v>
       </c>
       <c r="G63" s="2">
         <v>45871</v>
       </c>
       <c r="H63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B64" t="s">
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>9</v>
+        <v>48</v>
+      </c>
+      <c r="D64" s="2">
+        <v>45627</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45641</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45664</v>
       </c>
       <c r="G64" s="2">
-        <v>45871</v>
+        <v>45885</v>
       </c>
       <c r="H64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B65" t="s">
         <v>77</v>
       </c>
       <c r="C65" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2">
-        <v>45627</v>
-      </c>
-      <c r="E65" s="2">
-        <v>45641</v>
-      </c>
-      <c r="F65" s="2">
-        <v>45664</v>
+        <v>45597</v>
       </c>
       <c r="G65" s="2">
-        <v>45885</v>
+        <v>45892</v>
       </c>
       <c r="H65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B66" t="s">
         <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D66" s="2">
-        <v>45597</v>
+        <v>45627</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45661</v>
+      </c>
+      <c r="F66" s="2">
+        <v>45682</v>
       </c>
       <c r="G66" s="2">
-        <v>45892</v>
+        <v>45905</v>
       </c>
       <c r="H66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B67" t="s">
         <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
-      </c>
-      <c r="D67" s="2">
-        <v>45627</v>
-      </c>
-      <c r="E67" s="2">
-        <v>45661</v>
-      </c>
-      <c r="F67" s="2">
-        <v>45682</v>
+        <v>9</v>
       </c>
       <c r="G67" s="2">
-        <v>45905</v>
+        <v>45912</v>
       </c>
       <c r="H67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B68" t="s">
         <v>77</v>
@@ -2258,16 +2285,19 @@
       <c r="C68" t="s">
         <v>9</v>
       </c>
+      <c r="D68" s="2">
+        <v>45661</v>
+      </c>
       <c r="G68" s="2">
-        <v>45912</v>
+        <v>45920</v>
       </c>
       <c r="H68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B69" t="s">
         <v>77</v>
@@ -2276,18 +2306,18 @@
         <v>9</v>
       </c>
       <c r="D69" s="2">
-        <v>45661</v>
+        <v>45627</v>
       </c>
       <c r="G69" s="2">
-        <v>45920</v>
+        <v>45926</v>
       </c>
       <c r="H69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B70" t="s">
         <v>77</v>
@@ -2295,19 +2325,16 @@
       <c r="C70" t="s">
         <v>9</v>
       </c>
-      <c r="D70" s="2">
-        <v>45627</v>
-      </c>
       <c r="G70" s="2">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="H70" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B71" t="s">
         <v>77</v>
@@ -2316,52 +2343,55 @@
         <v>9</v>
       </c>
       <c r="G71" s="2">
-        <v>45927</v>
+        <v>45940</v>
       </c>
       <c r="H71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B72" t="s">
         <v>77</v>
       </c>
       <c r="C72" t="s">
         <v>9</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45940</v>
       </c>
       <c r="G72" s="2">
         <v>45940</v>
       </c>
       <c r="H72" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
         <v>9</v>
       </c>
-      <c r="F73" s="2">
-        <v>45940</v>
+      <c r="E73" s="2">
+        <v>45670</v>
       </c>
       <c r="G73" s="2">
-        <v>45940</v>
+        <v>45675</v>
       </c>
       <c r="H73" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B74" t="s">
         <v>153</v>
@@ -2369,19 +2399,16 @@
       <c r="C74" t="s">
         <v>9</v>
       </c>
-      <c r="E74" s="2">
-        <v>45670</v>
-      </c>
       <c r="G74" s="2">
-        <v>45675</v>
+        <v>45689</v>
       </c>
       <c r="H74" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B75" t="s">
         <v>153</v>
@@ -2389,16 +2416,19 @@
       <c r="C75" t="s">
         <v>9</v>
       </c>
+      <c r="E75" s="2">
+        <v>45693</v>
+      </c>
       <c r="G75" s="2">
-        <v>45689</v>
+        <v>45696</v>
       </c>
       <c r="H75" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B76" t="s">
         <v>153</v>
@@ -2406,19 +2436,16 @@
       <c r="C76" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="2">
-        <v>45693</v>
-      </c>
       <c r="G76" s="2">
-        <v>45696</v>
+        <v>45731</v>
       </c>
       <c r="H76" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B77" t="s">
         <v>153</v>
@@ -2426,16 +2453,19 @@
       <c r="C77" t="s">
         <v>9</v>
       </c>
+      <c r="E77" s="2">
+        <v>45870</v>
+      </c>
       <c r="G77" s="2">
-        <v>45731</v>
+        <v>45892</v>
       </c>
       <c r="H77" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B78" t="s">
         <v>153</v>
@@ -2444,18 +2474,18 @@
         <v>9</v>
       </c>
       <c r="E78" s="2">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="G78" s="2">
-        <v>45892</v>
+        <v>45906</v>
       </c>
       <c r="H78" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B79" t="s">
         <v>153</v>
@@ -2463,31 +2493,44 @@
       <c r="C79" t="s">
         <v>9</v>
       </c>
-      <c r="E79" s="2">
-        <v>45901</v>
-      </c>
       <c r="G79" s="2">
-        <v>45906</v>
+        <v>45920</v>
       </c>
       <c r="H79" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B80" t="s">
-        <v>153</v>
-      </c>
-      <c r="C80" t="s">
-        <v>9</v>
+      <c r="A80" t="s">
+        <v>168</v>
       </c>
       <c r="G80" s="2">
-        <v>45920</v>
+        <v>45657</v>
       </c>
       <c r="H80" t="s">
-        <v>167</v>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>170</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45710</v>
+      </c>
+      <c r="H81" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>172</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45927</v>
+      </c>
+      <c r="H82" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -2550,27 +2593,97 @@
     <hyperlink ref="A57" r:id="rId56" xr:uid="{A9C391CB-4299-43E7-AED3-C7CDDCF9BDF4}"/>
     <hyperlink ref="A58" r:id="rId57" xr:uid="{C515EE75-2747-4A8C-8C1B-AF8BFF85328A}"/>
     <hyperlink ref="A59" r:id="rId58" xr:uid="{B96914B8-56BF-460D-B5A1-4A4E0901C4CF}"/>
-    <hyperlink ref="A60" r:id="rId59" xr:uid="{2C15BD7B-64E8-41BB-8603-AE4865DA6A2D}"/>
-    <hyperlink ref="A61" r:id="rId60" xr:uid="{A30389F3-2FA6-47BA-8D91-E6CCA7529BEF}"/>
-    <hyperlink ref="A62" r:id="rId61" xr:uid="{ED184F75-EFC6-4914-B6D2-5BFB907EC7B2}"/>
-    <hyperlink ref="A63" r:id="rId62" xr:uid="{CF5C5B26-9A33-4D4C-B0D2-E7A84E3ED9BA}"/>
-    <hyperlink ref="A64" r:id="rId63" xr:uid="{2EC3CEE9-5FC4-4101-8CBF-729F343F8937}"/>
-    <hyperlink ref="A65" r:id="rId64" xr:uid="{EFE82A5B-461F-402C-8AAD-5E0E7790A16A}"/>
-    <hyperlink ref="A66" r:id="rId65" xr:uid="{BDBFB290-BC22-4E4D-B3E2-4F615957BFDE}"/>
-    <hyperlink ref="A67" r:id="rId66" xr:uid="{0C5BE74B-BA7E-4007-90DB-55CB10B94ADC}"/>
-    <hyperlink ref="A68" r:id="rId67" xr:uid="{0EBBF0D5-3AC3-4C01-AACC-9180836994E7}"/>
-    <hyperlink ref="A69" r:id="rId68" xr:uid="{38E29E62-AD1E-4104-B08A-7A89FA2CB079}"/>
-    <hyperlink ref="A70" r:id="rId69" xr:uid="{5AF90E1A-EBF8-4216-9C08-E2F1FC6B4C57}"/>
-    <hyperlink ref="A71" r:id="rId70" xr:uid="{74E1499C-078A-4DCD-8FFC-D3BFCDFCCD35}"/>
-    <hyperlink ref="A72" r:id="rId71" display="Kodiak Ultra" xr:uid="{47478C84-A3B7-40B6-84F2-E3DE5505CD04}"/>
-    <hyperlink ref="A73" r:id="rId72" xr:uid="{ABEB8C11-7EF3-4B2B-9FA2-4150C957E47C}"/>
-    <hyperlink ref="A74" r:id="rId73" xr:uid="{A6CCC76A-A845-403E-B201-0050E85FA7FB}"/>
-    <hyperlink ref="A75" r:id="rId74" xr:uid="{A4FB8691-C4AC-4ADA-8C8F-3A6BD97D5B2C}"/>
-    <hyperlink ref="A76" r:id="rId75" xr:uid="{99750AA6-8A60-4D39-AE74-38B75A5D3571}"/>
-    <hyperlink ref="A77" r:id="rId76" xr:uid="{FEC97E56-B757-4F40-A000-42944451E1E9}"/>
-    <hyperlink ref="A78" r:id="rId77" xr:uid="{82E80058-9EBD-4D60-9E6F-966E27E1309D}"/>
-    <hyperlink ref="A79" r:id="rId78" xr:uid="{9528B1CC-4B91-4978-ACBC-63395811AAB5}"/>
-    <hyperlink ref="A80" r:id="rId79" xr:uid="{B13F1EA1-B861-4503-9C25-0666D0A38ADB}"/>
+    <hyperlink ref="A60" r:id="rId59" xr:uid="{A30389F3-2FA6-47BA-8D91-E6CCA7529BEF}"/>
+    <hyperlink ref="A61" r:id="rId60" xr:uid="{ED184F75-EFC6-4914-B6D2-5BFB907EC7B2}"/>
+    <hyperlink ref="A62" r:id="rId61" xr:uid="{CF5C5B26-9A33-4D4C-B0D2-E7A84E3ED9BA}"/>
+    <hyperlink ref="A63" r:id="rId62" xr:uid="{2EC3CEE9-5FC4-4101-8CBF-729F343F8937}"/>
+    <hyperlink ref="A64" r:id="rId63" xr:uid="{EFE82A5B-461F-402C-8AAD-5E0E7790A16A}"/>
+    <hyperlink ref="A65" r:id="rId64" xr:uid="{BDBFB290-BC22-4E4D-B3E2-4F615957BFDE}"/>
+    <hyperlink ref="A66" r:id="rId65" xr:uid="{0C5BE74B-BA7E-4007-90DB-55CB10B94ADC}"/>
+    <hyperlink ref="A67" r:id="rId66" xr:uid="{0EBBF0D5-3AC3-4C01-AACC-9180836994E7}"/>
+    <hyperlink ref="A68" r:id="rId67" xr:uid="{38E29E62-AD1E-4104-B08A-7A89FA2CB079}"/>
+    <hyperlink ref="A69" r:id="rId68" xr:uid="{5AF90E1A-EBF8-4216-9C08-E2F1FC6B4C57}"/>
+    <hyperlink ref="A70" r:id="rId69" xr:uid="{74E1499C-078A-4DCD-8FFC-D3BFCDFCCD35}"/>
+    <hyperlink ref="A71" r:id="rId70" display="Kodiak Ultra" xr:uid="{47478C84-A3B7-40B6-84F2-E3DE5505CD04}"/>
+    <hyperlink ref="A72" r:id="rId71" xr:uid="{ABEB8C11-7EF3-4B2B-9FA2-4150C957E47C}"/>
+    <hyperlink ref="A73" r:id="rId72" xr:uid="{A6CCC76A-A845-403E-B201-0050E85FA7FB}"/>
+    <hyperlink ref="A74" r:id="rId73" xr:uid="{A4FB8691-C4AC-4ADA-8C8F-3A6BD97D5B2C}"/>
+    <hyperlink ref="A75" r:id="rId74" xr:uid="{99750AA6-8A60-4D39-AE74-38B75A5D3571}"/>
+    <hyperlink ref="A76" r:id="rId75" xr:uid="{FEC97E56-B757-4F40-A000-42944451E1E9}"/>
+    <hyperlink ref="A77" r:id="rId76" xr:uid="{82E80058-9EBD-4D60-9E6F-966E27E1309D}"/>
+    <hyperlink ref="A78" r:id="rId77" xr:uid="{9528B1CC-4B91-4978-ACBC-63395811AAB5}"/>
+    <hyperlink ref="A79" r:id="rId78" xr:uid="{B13F1EA1-B861-4503-9C25-0666D0A38ADB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{386E5D08-F90F-463A-AEBF-3CB34D775BB4}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2">
+        <v>45634</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2">
+        <v>45492</v>
+      </c>
+      <c r="H2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{2C15BD7B-64E8-41BB-8603-AE4865DA6A2D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
